--- a/output/Tables/Best practice/DALY_prev_fraction.xlsx
+++ b/output/Tables/Best practice/DALY_prev_fraction.xlsx
@@ -513,85 +513,85 @@
         </is>
       </c>
       <c r="C2">
-        <v>89193.30727630894</v>
+        <v>834249.4801747177</v>
       </c>
       <c r="D2">
-        <v>63407.50684374821</v>
+        <v>607553.2641292112</v>
       </c>
       <c r="E2">
-        <v>114986.7365413404</v>
+        <v>1059891.745615553</v>
       </c>
       <c r="F2">
-        <v>454860.3495975039</v>
+        <v>2417452.592684963</v>
       </c>
       <c r="G2">
-        <v>331465.232035532</v>
+        <v>1329843.997661838</v>
       </c>
       <c r="H2">
-        <v>627405.0740012391</v>
+        <v>4001899.113651286</v>
       </c>
       <c r="I2">
-        <v>958721911.2761286</v>
+        <v>10918173592.42197</v>
       </c>
       <c r="J2">
-        <v>491522731.3159365</v>
+        <v>8044948920.418863</v>
       </c>
       <c r="K2">
-        <v>1473296266.219188</v>
+        <v>13786464463.95169</v>
       </c>
       <c r="L2">
-        <v>60496426496.46802</v>
+        <v>321521194827.1001</v>
       </c>
       <c r="M2">
-        <v>44084875860.72575</v>
+        <v>176869251689.0245</v>
       </c>
       <c r="N2">
-        <v>83444874842.16479</v>
+        <v>532252582115.621</v>
       </c>
       <c r="O2">
-        <v>421214.3941698477</v>
+        <v>2894762.809937084</v>
       </c>
       <c r="P2">
-        <v>274975.6576435625</v>
+        <v>1848107.818410433</v>
       </c>
       <c r="Q2">
-        <v>551108.2542967909</v>
+        <v>3788140.850758359</v>
       </c>
       <c r="R2">
-        <v>1463407.025029395</v>
+        <v>7889762.712992449</v>
       </c>
       <c r="S2">
-        <v>897665.1386404218</v>
+        <v>3902046.741541974</v>
       </c>
       <c r="T2">
-        <v>2254431.012678022</v>
+        <v>13226700.51329626</v>
       </c>
       <c r="U2">
-        <v>4516283293.639452</v>
+        <v>39187854541.78131</v>
       </c>
       <c r="V2">
-        <v>1991501365.785143</v>
+        <v>25023131775.73364</v>
       </c>
       <c r="W2">
-        <v>6709110501.833838</v>
+        <v>51286936575.69694</v>
       </c>
       <c r="X2">
-        <v>194633134328.9095</v>
+        <v>1049338440827.996</v>
       </c>
       <c r="Y2">
-        <v>119389463439.1761</v>
+        <v>518972216625.0825</v>
       </c>
       <c r="Z2">
-        <v>299839324686.1771</v>
+        <v>1759151168268.403</v>
       </c>
       <c r="AA2">
-        <v>0.689177144965279</v>
+        <v>0.6935962866533326</v>
       </c>
       <c r="AB2">
-        <v>0.6307473491311473</v>
+        <v>0.6591932168561561</v>
       </c>
       <c r="AC2">
-        <v>0.7217013647909549</v>
+        <v>0.6974378372271799</v>
       </c>
     </row>
     <row r="3">
@@ -606,22 +606,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>41594.12233561477</v>
+        <v>384989.1662475551</v>
       </c>
       <c r="D3">
-        <v>29545.51206382153</v>
+        <v>276422.0106009928</v>
       </c>
       <c r="E3">
-        <v>51364.74233097701</v>
+        <v>492697.3526181864</v>
       </c>
       <c r="F3">
-        <v>122137.8781134041</v>
+        <v>1119403.991155143</v>
       </c>
       <c r="G3">
-        <v>53668.38116603896</v>
+        <v>489260.930662933</v>
       </c>
       <c r="H3">
-        <v>230476.4186145855</v>
+        <v>2206808.921707753</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -633,31 +633,31 @@
         <v>0</v>
       </c>
       <c r="L3">
-        <v>16244337789.08275</v>
+        <v>148880730823.634</v>
       </c>
       <c r="M3">
-        <v>7137894695.083182</v>
+        <v>65071703778.17009</v>
       </c>
       <c r="N3">
-        <v>30653363675.73988</v>
+        <v>293505586587.1311</v>
       </c>
       <c r="O3">
-        <v>240368.8630631386</v>
+        <v>1282525.778235175</v>
       </c>
       <c r="P3">
-        <v>185388.8581129597</v>
+        <v>818572.715849875</v>
       </c>
       <c r="Q3">
-        <v>286445.139676228</v>
+        <v>1678081.630463409</v>
       </c>
       <c r="R3">
-        <v>672362.6305331753</v>
+        <v>3564716.970122794</v>
       </c>
       <c r="S3">
-        <v>321118.1429979233</v>
+        <v>1406932.6904066</v>
       </c>
       <c r="T3">
-        <v>1223931.206653062</v>
+        <v>7125371.754365409</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -669,28 +669,28 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>89424229860.91232</v>
+        <v>474107357026.3315</v>
       </c>
       <c r="Y3">
-        <v>42708713018.7238</v>
+        <v>187122047824.0778</v>
       </c>
       <c r="Z3">
-        <v>162782850484.8573</v>
+        <v>947674443330.5994</v>
       </c>
       <c r="AA3">
-        <v>0.8183452313276984</v>
+        <v>0.6859767548062636</v>
       </c>
       <c r="AB3">
-        <v>0.8328702929551195</v>
+        <v>0.6522499377553465</v>
       </c>
       <c r="AC3">
-        <v>0.8116916887470811</v>
+        <v>0.6902885915593477</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -699,85 +699,85 @@
         </is>
       </c>
       <c r="C4">
-        <v>23097.45376066938</v>
+        <v>273837.4202767641</v>
       </c>
       <c r="D4">
-        <v>21917.06446397378</v>
+        <v>198414.3278513882</v>
       </c>
       <c r="E4">
-        <v>24339.53800611492</v>
+        <v>348820.2036360516</v>
       </c>
       <c r="F4">
-        <v>298521.5271842326</v>
+        <v>432043.4470685198</v>
       </c>
       <c r="G4">
-        <v>266122.2126181076</v>
+        <v>242241.4342008198</v>
       </c>
       <c r="H4">
-        <v>329454.2725148639</v>
+        <v>642663.4610034378</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>4054710682.038078</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2937920952.495499</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>5164980755.238992</v>
       </c>
       <c r="L4">
-        <v>39703363115.50294</v>
+        <v>57461778460.11314</v>
       </c>
       <c r="M4">
-        <v>35394254278.20831</v>
+        <v>32218110748.70904</v>
       </c>
       <c r="N4">
-        <v>43817418244.4769</v>
+        <v>85474240313.45721</v>
       </c>
       <c r="O4">
-        <v>56513.8995147949</v>
+        <v>936181.8281366293</v>
       </c>
       <c r="P4">
-        <v>48791.29002398933</v>
+        <v>597613.1732159001</v>
       </c>
       <c r="Q4">
-        <v>63731.18949027691</v>
+        <v>1225018.997874267</v>
       </c>
       <c r="R4">
-        <v>626899.9917475552</v>
+        <v>1382824.412304197</v>
       </c>
       <c r="S4">
-        <v>543005.5653916668</v>
+        <v>698105.1481779148</v>
       </c>
       <c r="T4">
-        <v>705418.2365733559</v>
+        <v>2088871.886616091</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>13862044329.21922</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>8848858255.807821</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>18138856301.52413</v>
       </c>
       <c r="X4">
-        <v>83377698902.42484</v>
+        <v>183915646836.4582</v>
       </c>
       <c r="Y4">
-        <v>72219740197.09169</v>
+        <v>92847984707.66267</v>
       </c>
       <c r="Z4">
-        <v>93820625464.25633</v>
+        <v>277819960919.9401</v>
       </c>
       <c r="AA4">
-        <v>0.52381315821672</v>
+        <v>0.6875644924805697</v>
       </c>
       <c r="AB4">
-        <v>0.5099088672762403</v>
+        <v>0.6530015072470376</v>
       </c>
       <c r="AC4">
-        <v>0.5329660399549307</v>
+        <v>0.6923394559900304</v>
       </c>
     </row>
     <row r="5">
@@ -792,91 +792,91 @@
         </is>
       </c>
       <c r="C5">
-        <v>11696.76815628306</v>
+        <v>79639.14226347416</v>
       </c>
       <c r="D5">
-        <v>7780.126950290891</v>
+        <v>60228.31205921528</v>
       </c>
       <c r="E5">
-        <v>16141.49420146841</v>
+        <v>99159.63273844472</v>
       </c>
       <c r="F5">
-        <v>12133.73789048171</v>
+        <v>81719.45139434267</v>
       </c>
       <c r="G5">
-        <v>6026.324169206112</v>
+        <v>46416.00403947769</v>
       </c>
       <c r="H5">
-        <v>20883.89291151867</v>
+        <v>126973.0843853021</v>
       </c>
       <c r="I5">
-        <v>651533379.8412814</v>
+        <v>4436059502.360087</v>
       </c>
       <c r="J5">
-        <v>433368631.3851057</v>
+        <v>3354837438.322411</v>
       </c>
       <c r="K5">
-        <v>899113510.0101956</v>
+        <v>5523389862.796827</v>
       </c>
       <c r="L5">
-        <v>1613787139.434067</v>
+        <v>10868687035.44757</v>
       </c>
       <c r="M5">
-        <v>801501114.5044129</v>
+        <v>6173328537.250532</v>
       </c>
       <c r="N5">
-        <v>2777557757.231983</v>
+        <v>16887420223.24518</v>
       </c>
       <c r="O5">
-        <v>47236.87893732829</v>
+        <v>307005.7300699163</v>
       </c>
       <c r="P5">
-        <v>33212.99389435949</v>
+        <v>196118.0198012635</v>
       </c>
       <c r="Q5">
-        <v>59718.82797233685</v>
+        <v>401902.073981562</v>
       </c>
       <c r="R5">
-        <v>42732.99898939581</v>
+        <v>278572.7295096618</v>
       </c>
       <c r="S5">
-        <v>23775.41224171267</v>
+        <v>139564.8094474466</v>
       </c>
       <c r="T5">
-        <v>65495.49338728898</v>
+        <v>444304.7376784908</v>
       </c>
       <c r="U5">
-        <v>2631188630.567058</v>
+        <v>17100833176.35455</v>
       </c>
       <c r="V5">
-        <v>1850030185.90361</v>
+        <v>10924165938.96986</v>
       </c>
       <c r="W5">
-        <v>3326458155.715104</v>
+        <v>22386749324.92086</v>
       </c>
       <c r="X5">
-        <v>5683488865.589643</v>
+        <v>37050173024.78503</v>
       </c>
       <c r="Y5">
-        <v>3162129828.147785</v>
+        <v>18562119656.5104</v>
       </c>
       <c r="Z5">
-        <v>8710900620.509434</v>
+        <v>59092530111.23927</v>
       </c>
       <c r="AA5">
-        <v>0.7160569541704129</v>
+        <v>0.706649493156837</v>
       </c>
       <c r="AB5">
-        <v>0.7465312437933986</v>
+        <v>0.6674232980129871</v>
       </c>
       <c r="AC5">
-        <v>0.6811400016787765</v>
+        <v>0.7142207282129348</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -885,91 +885,91 @@
         </is>
       </c>
       <c r="C6">
-        <v>7807.969906813774</v>
+        <v>52292.88987005932</v>
       </c>
       <c r="D6">
-        <v>1701.767435041758</v>
+        <v>40267.21649479034</v>
       </c>
       <c r="E6">
-        <v>15748.83198109786</v>
+        <v>64457.56901727636</v>
       </c>
       <c r="F6">
-        <v>12488.97347109676</v>
+        <v>700183.6535500182</v>
       </c>
       <c r="G6">
-        <v>2153.534940707273</v>
+        <v>505624.7052847089</v>
       </c>
       <c r="H6">
-        <v>29087.72122855713</v>
+        <v>893458.098147049</v>
       </c>
       <c r="I6">
-        <v>115612610.4101912</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>25198070.41066327</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>233192955.1441161</v>
+        <v>0</v>
       </c>
       <c r="L6">
-        <v>1661033471.655869</v>
+        <v>93124425922.15242</v>
       </c>
       <c r="M6">
-        <v>286420147.1140673</v>
+        <v>67248085802.86628</v>
       </c>
       <c r="N6">
-        <v>3868666923.398098</v>
+        <v>118829927053.5575</v>
       </c>
       <c r="O6">
-        <v>51293.52625405673</v>
+        <v>210769.2408234931</v>
       </c>
       <c r="P6">
-        <v>-2716.803399319634</v>
+        <v>134717.4247567642</v>
       </c>
       <c r="Q6">
-        <v>103161.8119143068</v>
+        <v>275966.008562903</v>
       </c>
       <c r="R6">
-        <v>76353.52739699572</v>
+        <v>2378994.283106449</v>
       </c>
       <c r="S6">
-        <v>-3318.852566345327</v>
+        <v>1518537.400400387</v>
       </c>
       <c r="T6">
-        <v>177306.9710400286</v>
+        <v>3112452.688807989</v>
       </c>
       <c r="U6">
-        <v>759503243.2438169</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>-40227707.93372593</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1527516949.015147</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>10155019143.80043</v>
+        <v>316406239653.1577</v>
       </c>
       <c r="Y6">
-        <v>-441407391.3239285</v>
+        <v>201965474253.2515</v>
       </c>
       <c r="Z6">
-        <v>23581827148.3238</v>
+        <v>413956207611.4626</v>
       </c>
       <c r="AA6">
-        <v>0.8364322658446274</v>
+        <v>0.7056808170906024</v>
       </c>
       <c r="AB6">
-        <v>1.648879363471911</v>
+        <v>0.6670317733686424</v>
       </c>
       <c r="AC6">
-        <v>0.8359471088026746</v>
+        <v>0.7129408259409635</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -978,91 +978,91 @@
         </is>
       </c>
       <c r="C7">
-        <v>3156.213946770902</v>
+        <v>29043.91197939255</v>
       </c>
       <c r="D7">
-        <v>2609.004754778901</v>
+        <v>20726.06188015699</v>
       </c>
       <c r="E7">
-        <v>3682.289309750315</v>
+        <v>37285.2357976984</v>
       </c>
       <c r="F7">
-        <v>5907.255698169928</v>
+        <v>57597.60709435066</v>
       </c>
       <c r="G7">
-        <v>3711.411674080375</v>
+        <v>30316.17848299707</v>
       </c>
       <c r="H7">
-        <v>8109.696288986516</v>
+        <v>94296.27530055412</v>
       </c>
       <c r="I7">
-        <v>53147486.64967524</v>
+        <v>2184131224.762307</v>
       </c>
       <c r="J7">
-        <v>43933031.06572188</v>
+        <v>1558620579.449674</v>
       </c>
       <c r="K7">
-        <v>62006069.68688547</v>
+        <v>2803887017.222727</v>
       </c>
       <c r="L7">
-        <v>785665007.8566004</v>
+        <v>7660481743.548637</v>
       </c>
       <c r="M7">
-        <v>493617752.6526899</v>
+        <v>4032051738.23861</v>
       </c>
       <c r="N7">
-        <v>1078589606.435207</v>
+        <v>12541404614.9737</v>
       </c>
       <c r="O7">
-        <v>13959.1961673284</v>
+        <v>95262.26308635654</v>
       </c>
       <c r="P7">
-        <v>10157.64026548246</v>
+        <v>60791.47842147082</v>
       </c>
       <c r="Q7">
-        <v>17243.39989211399</v>
+        <v>124614.6342804619</v>
       </c>
       <c r="R7">
-        <v>22032.68308364361</v>
+        <v>184422.1113187462</v>
       </c>
       <c r="S7">
-        <v>12872.55829590665</v>
+        <v>87566.05762275173</v>
       </c>
       <c r="T7">
-        <v>30959.63200922539</v>
+        <v>306250.8394600226</v>
       </c>
       <c r="U7">
-        <v>235058904.2616436</v>
+        <v>7163817446.357061</v>
       </c>
       <c r="V7">
-        <v>171044504.4304591</v>
+        <v>4571579968.773042</v>
       </c>
       <c r="W7">
-        <v>290361610.7833073</v>
+        <v>9371145112.525038</v>
       </c>
       <c r="X7">
-        <v>2930346850.1246</v>
+        <v>24528140805.39325</v>
       </c>
       <c r="Y7">
-        <v>1712050253.355584</v>
+        <v>11646285663.82598</v>
       </c>
       <c r="Z7">
-        <v>4117631057.226976</v>
+        <v>40731361648.183</v>
       </c>
       <c r="AA7">
-        <v>0.7318866850785279</v>
+        <v>0.6876860009763051</v>
       </c>
       <c r="AB7">
-        <v>0.7116803366693185</v>
+        <v>0.6537907574461795</v>
       </c>
       <c r="AC7">
-        <v>0.7380557919238194</v>
+        <v>0.6920946389344889</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1071,85 +1071,85 @@
         </is>
       </c>
       <c r="C8">
-        <v>1840.779170157067</v>
+        <v>14446.94953747251</v>
       </c>
       <c r="D8">
-        <v>-145.9688241586456</v>
+        <v>11495.33524266757</v>
       </c>
       <c r="E8">
-        <v>3709.840711931893</v>
+        <v>17471.75180789518</v>
       </c>
       <c r="F8">
-        <v>3670.977240118758</v>
+        <v>26504.44242258856</v>
       </c>
       <c r="G8">
-        <v>-216.6325326082901</v>
+        <v>15984.74499090185</v>
       </c>
       <c r="H8">
-        <v>9393.07244272732</v>
+        <v>37699.27310719046</v>
       </c>
       <c r="I8">
-        <v>138428434.3749808</v>
+        <v>243272183.261501</v>
       </c>
       <c r="J8">
-        <v>-10977001.54555432</v>
+        <v>193569950.1512797</v>
       </c>
       <c r="K8">
-        <v>278983731.377991</v>
+        <v>294206828.6931463</v>
       </c>
       <c r="L8">
-        <v>488239972.9357948</v>
+        <v>3525090842.204278</v>
       </c>
       <c r="M8">
-        <v>-28812126.83690259</v>
+        <v>2125971083.789947</v>
       </c>
       <c r="N8">
-        <v>1249278634.882734</v>
+        <v>5014003323.256331</v>
       </c>
       <c r="O8">
-        <v>11842.03023320078</v>
+        <v>63017.96958551427</v>
       </c>
       <c r="P8">
-        <v>141.6787460911411</v>
+        <v>40295.00636515921</v>
       </c>
       <c r="Q8">
-        <v>20807.88535152832</v>
+        <v>82557.50559575506</v>
       </c>
       <c r="R8">
-        <v>23025.19327862965</v>
+        <v>100232.2066306015</v>
       </c>
       <c r="S8">
-        <v>212.3122795577478</v>
+        <v>51340.63548687388</v>
       </c>
       <c r="T8">
-        <v>51319.47301506125</v>
+        <v>149448.6063682592</v>
       </c>
       <c r="U8">
-        <v>890532515.5669334</v>
+        <v>1061159589.850477</v>
       </c>
       <c r="V8">
-        <v>10654383.38479992</v>
+        <v>678527612.1829165</v>
       </c>
       <c r="W8">
-        <v>1564773786.32028</v>
+        <v>1390185836.726909</v>
       </c>
       <c r="X8">
-        <v>3062350706.057743</v>
+        <v>13330883481.87</v>
       </c>
       <c r="Y8">
-        <v>28237533.18118046</v>
+        <v>6828304519.754226</v>
       </c>
       <c r="Z8">
-        <v>6825489911.003146</v>
+        <v>19876664646.97848</v>
       </c>
       <c r="AA8">
-        <v>0.8405669305053826</v>
+        <v>0.7355696006946275</v>
       </c>
       <c r="AB8">
-        <v>2.020348578327837</v>
+        <v>0.6886531528229987</v>
       </c>
       <c r="AC8">
-        <v>0.8169686496981245</v>
+        <v>0.7477442311218685</v>
       </c>
     </row>
     <row r="9">
@@ -1164,85 +1164,85 @@
         </is>
       </c>
       <c r="C9">
-        <v>68719.94143307832</v>
+        <v>651062.7327694993</v>
       </c>
       <c r="D9">
-        <v>51685.65041206853</v>
+        <v>514474.455322087</v>
       </c>
       <c r="E9">
-        <v>85990.4344833042</v>
+        <v>790629.6520979484</v>
       </c>
       <c r="F9">
-        <v>358403.7633553839</v>
+        <v>1869607.557437559</v>
       </c>
       <c r="G9">
-        <v>284793.2449330802</v>
+        <v>1115268.732323369</v>
       </c>
       <c r="H9">
-        <v>470294.2396495104</v>
+        <v>2968368.109029017</v>
       </c>
       <c r="I9">
-        <v>733961399.4069113</v>
+        <v>8549267258.579318</v>
       </c>
       <c r="J9">
-        <v>420385539.1279265</v>
+        <v>6862329778.482424</v>
       </c>
       <c r="K9">
-        <v>1084051170.179314</v>
+        <v>10285154201.89912</v>
       </c>
       <c r="L9">
-        <v>47667700526.26606</v>
+        <v>248657805139.1954</v>
       </c>
       <c r="M9">
-        <v>37877501576.09967</v>
+        <v>148330741399.0081</v>
       </c>
       <c r="N9">
-        <v>62549133873.38487</v>
+        <v>394792958500.8593</v>
       </c>
       <c r="O9">
-        <v>405569.5486771298</v>
+        <v>2775401.592423047</v>
       </c>
       <c r="P9">
-        <v>264544.9892755263</v>
+        <v>1771926.780446545</v>
       </c>
       <c r="Q9">
-        <v>530754.9676267686</v>
+        <v>3629675.923693352</v>
       </c>
       <c r="R9">
-        <v>1410603.46417355</v>
+        <v>7568830.837991592</v>
       </c>
       <c r="S9">
-        <v>867351.2949004002</v>
+        <v>3751531.470255754</v>
       </c>
       <c r="T9">
-        <v>2169487.215998353</v>
+        <v>12654421.21214452</v>
       </c>
       <c r="U9">
-        <v>4353033041.809611</v>
+        <v>37801260758.09966</v>
       </c>
       <c r="V9">
-        <v>1912735811.523089</v>
+        <v>24142630787.81494</v>
       </c>
       <c r="W9">
-        <v>6464836695.780928</v>
+        <v>49441315001.58229</v>
       </c>
       <c r="X9">
-        <v>187610260735.0822</v>
+        <v>1006654501452.882</v>
       </c>
       <c r="Y9">
-        <v>115357722221.7532</v>
+        <v>498953685544.0153</v>
       </c>
       <c r="Z9">
-        <v>288541799727.781</v>
+        <v>1683038021215.221</v>
       </c>
       <c r="AA9">
-        <v>0.7459216764610976</v>
+        <v>0.7529859502139878</v>
       </c>
       <c r="AB9">
-        <v>0.6716517902174993</v>
+        <v>0.7027164129727165</v>
       </c>
       <c r="AC9">
-        <v>0.7832233183116082</v>
+        <v>0.7654283780138235</v>
       </c>
     </row>
     <row r="10">
@@ -1257,22 +1257,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>30664.03333429497</v>
+        <v>299102.6479928473</v>
       </c>
       <c r="D10">
-        <v>21781.55267933359</v>
+        <v>232189.9361119196</v>
       </c>
       <c r="E10">
-        <v>37867.13320540302</v>
+        <v>367001.6792238866</v>
       </c>
       <c r="F10">
-        <v>89881.34818002082</v>
+        <v>864682.1518575784</v>
       </c>
       <c r="G10">
-        <v>39494.59846816665</v>
+        <v>406391.3249949201</v>
       </c>
       <c r="H10">
-        <v>169607.7543573139</v>
+        <v>1641062.240329425</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -1284,31 +1284,31 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>11954219307.94277</v>
+        <v>115002726197.0579</v>
       </c>
       <c r="M10">
-        <v>5252781596.266165</v>
+        <v>54050046224.32437</v>
       </c>
       <c r="N10">
-        <v>22557831329.52275</v>
+        <v>218261277963.8136</v>
       </c>
       <c r="O10">
-        <v>231716.1558831894</v>
+        <v>1222367.374760105</v>
       </c>
       <c r="P10">
-        <v>179051.8827354544</v>
+        <v>780052.806066409</v>
       </c>
       <c r="Q10">
-        <v>275934.5064710245</v>
+        <v>1598378.627405813</v>
       </c>
       <c r="R10">
-        <v>643756.1284944944</v>
+        <v>3375300.822845115</v>
       </c>
       <c r="S10">
-        <v>307981.8178954474</v>
+        <v>1331617.897367873</v>
       </c>
       <c r="T10">
-        <v>1171002.773335992</v>
+        <v>6743203.258185442</v>
       </c>
       <c r="U10">
         <v>0</v>
@@ -1320,28 +1320,28 @@
         <v>0</v>
       </c>
       <c r="X10">
-        <v>85619565089.76775</v>
+        <v>448915009438.4003</v>
       </c>
       <c r="Y10">
-        <v>40961581780.0945</v>
+        <v>177105180349.9272</v>
       </c>
       <c r="Z10">
-        <v>155743368853.687</v>
+        <v>896846033338.6637</v>
       </c>
       <c r="AA10">
-        <v>0.8603798174469891</v>
+        <v>0.743820714881135</v>
       </c>
       <c r="AB10">
-        <v>0.8717632140168283</v>
+        <v>0.6948138607942949</v>
       </c>
       <c r="AC10">
-        <v>0.8551602453731775</v>
+        <v>0.7566346174813324</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1350,85 +1350,85 @@
         </is>
       </c>
       <c r="C11">
-        <v>19370.12329902716</v>
+        <v>212525.446249702</v>
       </c>
       <c r="D11">
-        <v>19826.25779759773</v>
+        <v>167472.2715808359</v>
       </c>
       <c r="E11">
-        <v>19156.98907776078</v>
+        <v>258510.1611876505</v>
       </c>
       <c r="F11">
-        <v>242900.6353347943</v>
+        <v>334246.975272383</v>
       </c>
       <c r="G11">
-        <v>235684.1781095685</v>
+        <v>202682.5883860864</v>
       </c>
       <c r="H11">
-        <v>251450.3891341221</v>
+        <v>477023.5892493287</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>3146864282.619343</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>2479761925.29746</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>3827759956.705527</v>
       </c>
       <c r="L11">
-        <v>32305784499.52764</v>
+        <v>44454847711.22694</v>
       </c>
       <c r="M11">
-        <v>31345995688.57261</v>
+        <v>26956784255.34949</v>
       </c>
       <c r="N11">
-        <v>33442901754.83824</v>
+        <v>63444137370.16071</v>
       </c>
       <c r="O11">
-        <v>53978.99272727947</v>
+        <v>903896.9432947705</v>
       </c>
       <c r="P11">
-        <v>46708.48497474167</v>
+        <v>577016.7305555792</v>
       </c>
       <c r="Q11">
-        <v>60786.27397847559</v>
+        <v>1182059.100727383</v>
       </c>
       <c r="R11">
-        <v>607383.9142757314</v>
+        <v>1334026.49933925</v>
       </c>
       <c r="S11">
-        <v>527101.4735638894</v>
+        <v>673255.3169188456</v>
       </c>
       <c r="T11">
-        <v>682634.4046139821</v>
+        <v>2013980.005359921</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>13384002039.36579</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>8543886729.336502</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>17502749104.47045</v>
       </c>
       <c r="X11">
-        <v>80782060598.67229</v>
+        <v>177425524412.1203</v>
       </c>
       <c r="Y11">
-        <v>70104495983.99728</v>
+        <v>89542957150.20647</v>
       </c>
       <c r="Z11">
-        <v>90790375813.65962</v>
+        <v>267859340712.8694</v>
       </c>
       <c r="AA11">
-        <v>0.6000871448424204</v>
+        <v>0.7494450256888172</v>
       </c>
       <c r="AB11">
-        <v>0.5528675408246577</v>
+        <v>0.6989513735834071</v>
       </c>
       <c r="AC11">
-        <v>0.6316470610995457</v>
+        <v>0.7631438306339694</v>
       </c>
     </row>
     <row r="12">
@@ -1443,91 +1443,91 @@
         </is>
       </c>
       <c r="C12">
-        <v>9090.7557443195</v>
+        <v>63287.78248113526</v>
       </c>
       <c r="D12">
-        <v>6674.16140322043</v>
+        <v>52111.61602501425</v>
       </c>
       <c r="E12">
-        <v>11920.27196069442</v>
+        <v>74946.15772170122</v>
       </c>
       <c r="F12">
-        <v>9175.574388626885</v>
+        <v>63276.76337032349</v>
       </c>
       <c r="G12">
-        <v>5059.28097278613</v>
+        <v>39386.95153463051</v>
       </c>
       <c r="H12">
-        <v>15026.35384012389</v>
+        <v>93470.44800518264</v>
       </c>
       <c r="I12">
-        <v>506373276.4700844</v>
+        <v>3525256059.764159</v>
       </c>
       <c r="J12">
-        <v>371764138.4821846</v>
+        <v>2902721235.825336</v>
       </c>
       <c r="K12">
-        <v>663982988.7546004</v>
+        <v>4174650877.414178</v>
       </c>
       <c r="L12">
-        <v>1220351393.687376</v>
+        <v>8415809528.253024</v>
       </c>
       <c r="M12">
-        <v>672884369.3805554</v>
+        <v>5238464554.105858</v>
       </c>
       <c r="N12">
-        <v>1998505060.736477</v>
+        <v>12431569584.68929</v>
       </c>
       <c r="O12">
-        <v>45191.80900532119</v>
+        <v>295218.8548246627</v>
       </c>
       <c r="P12">
-        <v>32037.13558413629</v>
+        <v>188665.8358090796</v>
       </c>
       <c r="Q12">
-        <v>56868.77249776782</v>
+        <v>386215.556131683</v>
       </c>
       <c r="R12">
-        <v>41571.96095689302</v>
+        <v>272293.7709899102</v>
       </c>
       <c r="S12">
-        <v>23318.47963966112</v>
+        <v>136428.7570856202</v>
       </c>
       <c r="T12">
-        <v>63409.8285206935</v>
+        <v>434038.8069771477</v>
       </c>
       <c r="U12">
-        <v>2517274145.214404</v>
+        <v>16444280651.44344</v>
       </c>
       <c r="V12">
-        <v>1784532526.307562</v>
+        <v>10509064386.23731</v>
       </c>
       <c r="W12">
-        <v>3167704365.670654</v>
+        <v>21512978907.64698</v>
       </c>
       <c r="X12">
-        <v>5529070807.266772</v>
+        <v>36215071541.65805</v>
       </c>
       <c r="Y12">
-        <v>3101357792.074929</v>
+        <v>18145024692.38748</v>
       </c>
       <c r="Z12">
-        <v>8433507193.252236</v>
+        <v>57727161327.96065</v>
       </c>
       <c r="AA12">
-        <v>0.7792845423351268</v>
+        <v>0.7676158248487138</v>
       </c>
       <c r="AB12">
-        <v>0.7830355558781338</v>
+        <v>0.7113002245566747</v>
       </c>
       <c r="AC12">
-        <v>0.7630280006951902</v>
+        <v>0.7846495601253832</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1536,91 +1536,91 @@
         </is>
       </c>
       <c r="C13">
-        <v>5725.28207245823</v>
+        <v>41916.39684632578</v>
       </c>
       <c r="D13">
-        <v>1247.840181714227</v>
+        <v>35077.8679945683</v>
       </c>
       <c r="E13">
-        <v>11548.0088268336</v>
+        <v>49124.48106016488</v>
       </c>
       <c r="F13">
-        <v>9169.256039678527</v>
+        <v>541865.3030779496</v>
       </c>
       <c r="G13">
-        <v>1581.099784336773</v>
+        <v>427590.883842962</v>
       </c>
       <c r="H13">
-        <v>21355.85956465411</v>
+        <v>658577.2451518901</v>
       </c>
       <c r="I13">
-        <v>84774251.64688888</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>18476769.5706426</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>170991366.698925</v>
+        <v>0</v>
       </c>
       <c r="L13">
-        <v>1219511053.277244</v>
+        <v>72068085309.36729</v>
       </c>
       <c r="M13">
-        <v>210286271.3167908</v>
+        <v>56869587551.11395</v>
       </c>
       <c r="N13">
-        <v>2840329322.098996</v>
+        <v>87590773605.20139</v>
       </c>
       <c r="O13">
-        <v>50097.17071623793</v>
+        <v>201898.9614152511</v>
       </c>
       <c r="P13">
-        <v>-2820.101415203864</v>
+        <v>129081.3530391022</v>
       </c>
       <c r="Q13">
-        <v>100762.5465009056</v>
+        <v>264183.1502992219</v>
       </c>
       <c r="R13">
-        <v>74619.37445955064</v>
+        <v>2313109.080426413</v>
       </c>
       <c r="S13">
-        <v>-3469.947666282956</v>
+        <v>1476484.828920645</v>
       </c>
       <c r="T13">
-        <v>173288.7035031838</v>
+        <v>3024652.489304188</v>
       </c>
       <c r="U13">
-        <v>741788806.7953339</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>-41757241.65492348</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>1491991026.038915</v>
+        <v>0</v>
       </c>
       <c r="X13">
-        <v>9924376803.120235</v>
+        <v>307643507696.713</v>
       </c>
       <c r="Y13">
-        <v>-461503039.6156332</v>
+        <v>196372482246.4458</v>
       </c>
       <c r="Z13">
-        <v>23047397565.92344</v>
+        <v>402278781077.457</v>
       </c>
       <c r="AA13">
-        <v>0.8771196340616745</v>
+        <v>0.7657415693608108</v>
       </c>
       <c r="AB13">
-        <v>1.455655224918843</v>
+        <v>0.7103994057591883</v>
       </c>
       <c r="AC13">
-        <v>0.8767613864439713</v>
+        <v>0.7822635005241896</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1629,91 +1629,91 @@
         </is>
       </c>
       <c r="C14">
-        <v>2539.237373239866</v>
+        <v>22287.45097384628</v>
       </c>
       <c r="D14">
-        <v>2261.3441742655</v>
+        <v>17386.43125552672</v>
       </c>
       <c r="E14">
-        <v>2816.569780577678</v>
+        <v>27270.31327301613</v>
       </c>
       <c r="F14">
-        <v>4607.211774132114</v>
+        <v>44244.9059353421</v>
       </c>
       <c r="G14">
-        <v>3131.634754774218</v>
+        <v>25279.45075175902</v>
       </c>
       <c r="H14">
-        <v>6022.72107678557</v>
+        <v>69362.18778621539</v>
       </c>
       <c r="I14">
-        <v>42758218.12798602</v>
+        <v>1676038600.68422</v>
       </c>
       <c r="J14">
-        <v>38078774.55045669</v>
+        <v>1307477016.846878</v>
       </c>
       <c r="K14">
-        <v>47428218.53514769</v>
+        <v>2050754828.444095</v>
       </c>
       <c r="L14">
-        <v>612759165.9595711</v>
+        <v>5884572489.400498</v>
       </c>
       <c r="M14">
-        <v>416507422.384971</v>
+        <v>3362166949.98395</v>
       </c>
       <c r="N14">
-        <v>801021903.2124809</v>
+        <v>9225170975.566647</v>
       </c>
       <c r="O14">
-        <v>12934.41118488275</v>
+        <v>92750.80380844926</v>
       </c>
       <c r="P14">
-        <v>9415.914686372307</v>
+        <v>59189.9430535955</v>
       </c>
       <c r="Q14">
-        <v>15975.9909843251</v>
+        <v>121266.0435217691</v>
       </c>
       <c r="R14">
-        <v>20869.11905234802</v>
+        <v>177570.4394420838</v>
       </c>
       <c r="S14">
-        <v>12194.97151108709</v>
+        <v>84299.88584708239</v>
       </c>
       <c r="T14">
-        <v>29325.37992707074</v>
+        <v>294730.709853746</v>
       </c>
       <c r="U14">
-        <v>217802549.9422402</v>
+        <v>6974953197.199179</v>
       </c>
       <c r="V14">
-        <v>158554587.4038234</v>
+        <v>4451142907.57344</v>
       </c>
       <c r="W14">
-        <v>269019712.1850498</v>
+        <v>9119327738.880478</v>
       </c>
       <c r="X14">
-        <v>2775592833.962287</v>
+        <v>23616868445.79714</v>
       </c>
       <c r="Y14">
-        <v>1621931210.974584</v>
+        <v>11211884817.66196</v>
       </c>
       <c r="Z14">
-        <v>3900275530.300409</v>
+        <v>39199184410.54822</v>
       </c>
       <c r="AA14">
-        <v>0.779233049436567</v>
+        <v>0.7508318046947619</v>
       </c>
       <c r="AB14">
-        <v>0.7432027822347036</v>
+        <v>0.7001247332930529</v>
       </c>
       <c r="AC14">
-        <v>0.7946242779543362</v>
+        <v>0.7646591092572779</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1722,85 +1722,85 @@
         </is>
       </c>
       <c r="C15">
-        <v>1330.50960973859</v>
+        <v>11943.00822564268</v>
       </c>
       <c r="D15">
-        <v>-105.5058240629434</v>
+        <v>10236.33235422225</v>
       </c>
       <c r="E15">
-        <v>2681.461632034695</v>
+        <v>13776.85963152902</v>
       </c>
       <c r="F15">
-        <v>2669.737638131259</v>
+        <v>21291.45792398265</v>
       </c>
       <c r="G15">
-        <v>-157.5471565520639</v>
+        <v>13937.53281301116</v>
       </c>
       <c r="H15">
-        <v>6831.16167651077</v>
+        <v>28872.39850697506</v>
       </c>
       <c r="I15">
-        <v>100055653.1619519</v>
+        <v>201108315.511596</v>
       </c>
       <c r="J15">
-        <v>-7934143.475357383</v>
+        <v>172369600.5127487</v>
       </c>
       <c r="K15">
-        <v>201648596.1906414</v>
+        <v>231988539.335317</v>
       </c>
       <c r="L15">
-        <v>355075105.8714574</v>
+        <v>2831763903.889693</v>
       </c>
       <c r="M15">
-        <v>-20953771.8214245</v>
+        <v>1853691864.130485</v>
       </c>
       <c r="N15">
-        <v>908544502.9759325</v>
+        <v>3840029001.427683</v>
       </c>
       <c r="O15">
-        <v>11651.00916021903</v>
+        <v>59268.65431980818</v>
       </c>
       <c r="P15">
-        <v>151.672710025489</v>
+        <v>37920.11192277947</v>
       </c>
       <c r="Q15">
-        <v>20426.8771942701</v>
+        <v>77573.44560748234</v>
       </c>
       <c r="R15">
-        <v>22402.96693453318</v>
+        <v>96530.22494881996</v>
       </c>
       <c r="S15">
-        <v>224.4999565980998</v>
+        <v>49444.78411568752</v>
       </c>
       <c r="T15">
-        <v>49826.12609743083</v>
+        <v>143815.9424640743</v>
       </c>
       <c r="U15">
-        <v>876167539.8576332</v>
+        <v>998024870.0912468</v>
       </c>
       <c r="V15">
-        <v>11405939.46662686</v>
+        <v>638536764.6676838</v>
       </c>
       <c r="W15">
-        <v>1536121591.886309</v>
+        <v>1306259250.584385</v>
       </c>
       <c r="X15">
-        <v>2979594602.292913</v>
+        <v>12838519918.19305</v>
       </c>
       <c r="Y15">
-        <v>29858494.22754727</v>
+        <v>6576156287.38644</v>
       </c>
       <c r="Z15">
-        <v>6626874770.958301</v>
+        <v>19127520347.72188</v>
       </c>
       <c r="AA15">
-        <v>0.8808310682271295</v>
+        <v>0.7794322147775857</v>
       </c>
       <c r="AB15">
-        <v>1.701769207172299</v>
+        <v>0.7181192503459803</v>
       </c>
       <c r="AC15">
-        <v>0.8629000042436973</v>
+        <v>0.7992406265099052</v>
       </c>
     </row>
     <row r="16">
@@ -1815,85 +1815,85 @@
         </is>
       </c>
       <c r="C16">
-        <v>120955.3166028246</v>
+        <v>1107759.2252712</v>
       </c>
       <c r="D16">
-        <v>81512.42349570108</v>
+        <v>729765.24728896</v>
       </c>
       <c r="E16">
-        <v>159678.3187043832</v>
+        <v>1474506.756121573</v>
       </c>
       <c r="F16">
-        <v>607919.035550802</v>
+        <v>3432563.884174273</v>
       </c>
       <c r="G16">
-        <v>391345.2328920255</v>
+        <v>1678737.129700258</v>
       </c>
       <c r="H16">
-        <v>901326.869796087</v>
+        <v>6020677.452664553</v>
       </c>
       <c r="I16">
-        <v>1208382559.95846</v>
+        <v>13638620896.11079</v>
       </c>
       <c r="J16">
-        <v>537587256.571039</v>
+        <v>9136237083.824625</v>
       </c>
       <c r="K16">
-        <v>1929811977.350922</v>
+        <v>18025086773.5994</v>
       </c>
       <c r="L16">
-        <v>80853231728.25667</v>
+        <v>456530996595.1784</v>
       </c>
       <c r="M16">
-        <v>52048915974.63939</v>
+        <v>223272038250.1344</v>
       </c>
       <c r="N16">
-        <v>119876473682.8796</v>
+        <v>800750101204.3855</v>
       </c>
       <c r="O16">
-        <v>360725.7794256359</v>
+        <v>2523951.338870222</v>
       </c>
       <c r="P16">
-        <v>235681.2757739804</v>
+        <v>1617167.658452089</v>
       </c>
       <c r="Q16">
-        <v>472127.8975950318</v>
+        <v>3305865.962827697</v>
       </c>
       <c r="R16">
-        <v>1322779.76793264</v>
+        <v>7231405.129795966</v>
       </c>
       <c r="S16">
-        <v>807323.9331739176</v>
+        <v>3558029.79711109</v>
       </c>
       <c r="T16">
-        <v>2046306.942823823</v>
+        <v>12227351.12085755</v>
       </c>
       <c r="U16">
-        <v>3732821445.353777</v>
+        <v>32999329825.94008</v>
       </c>
       <c r="V16">
-        <v>1600831949.937253</v>
+        <v>21138050889.27472</v>
       </c>
       <c r="W16">
-        <v>5606158752.723078</v>
+        <v>43230687945.89658</v>
       </c>
       <c r="X16">
-        <v>175929709135.0412</v>
+        <v>961776882262.8634</v>
       </c>
       <c r="Y16">
-        <v>107374083112.131</v>
+        <v>473217963015.775</v>
       </c>
       <c r="Z16">
-        <v>272158823395.5685</v>
+        <v>1626237699074.054</v>
       </c>
       <c r="AA16">
-        <v>0.54042309212144</v>
+        <v>0.5253254626779398</v>
       </c>
       <c r="AB16">
-        <v>0.5152562474476772</v>
+        <v>0.528183510137185</v>
       </c>
       <c r="AC16">
-        <v>0.5595348620807143</v>
+        <v>0.5076057444367967</v>
       </c>
     </row>
     <row r="17">
@@ -1908,22 +1908,22 @@
         </is>
       </c>
       <c r="C17">
-        <v>64101.02771560722</v>
+        <v>542460.2195339629</v>
       </c>
       <c r="D17">
-        <v>45802.08742320828</v>
+        <v>351263.6144924493</v>
       </c>
       <c r="E17">
-        <v>79077.29581720218</v>
+        <v>727299.4190330927</v>
       </c>
       <c r="F17">
-        <v>202792.6162261039</v>
+        <v>1694501.330409928</v>
       </c>
       <c r="G17">
-        <v>89750.98252888114</v>
+        <v>667473.8853996802</v>
       </c>
       <c r="H17">
-        <v>382194.3147598401</v>
+        <v>3495414.942015618</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1935,31 +1935,31 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>26971417958.07182</v>
+        <v>225368676944.5204</v>
       </c>
       <c r="M17">
-        <v>11936880676.34119</v>
+        <v>88774026758.15747</v>
       </c>
       <c r="N17">
-        <v>50831843863.05874</v>
+        <v>464890187288.0771</v>
       </c>
       <c r="O17">
-        <v>210437.8905157994</v>
+        <v>1165083.994412385</v>
       </c>
       <c r="P17">
-        <v>161461.0198051779</v>
+        <v>746527.0937947494</v>
       </c>
       <c r="Q17">
-        <v>251275.0084889801</v>
+        <v>1525664.379200442</v>
       </c>
       <c r="R17">
-        <v>619284.1380716657</v>
+        <v>3417349.805180832</v>
       </c>
       <c r="S17">
-        <v>294078.6896811156</v>
+        <v>1354642.021140593</v>
       </c>
       <c r="T17">
-        <v>1129681.966296552</v>
+        <v>6836311.544284264</v>
       </c>
       <c r="U17">
         <v>0</v>
@@ -1971,28 +1971,28 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>82364790363.53154</v>
+        <v>454507524089.0507</v>
       </c>
       <c r="Y17">
-        <v>39112465727.58837</v>
+        <v>180167388811.6988</v>
       </c>
       <c r="Z17">
-        <v>150247701517.4414</v>
+        <v>909229435389.807</v>
       </c>
       <c r="AA17">
-        <v>0.6725370411430818</v>
+        <v>0.5041475333192407</v>
       </c>
       <c r="AB17">
-        <v>0.6948062349359531</v>
+        <v>0.5072691714984043</v>
       </c>
       <c r="AC17">
-        <v>0.6616797238847746</v>
+        <v>0.4886987055266548</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mort</t>
+          <t>cancer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2001,85 +2001,85 @@
         </is>
       </c>
       <c r="C18">
-        <v>25363.65647208407</v>
+        <v>356886.7559033735</v>
       </c>
       <c r="D18">
-        <v>22396.77597872159</v>
+        <v>233590.4753474353</v>
       </c>
       <c r="E18">
-        <v>28179.89918589521</v>
+        <v>476432.2218682657</v>
       </c>
       <c r="F18">
-        <v>356593.1631501114</v>
+        <v>613543.4162822388</v>
       </c>
       <c r="G18">
-        <v>287714.6906993586</v>
+        <v>309083.097915557</v>
       </c>
       <c r="H18">
-        <v>419811.331003999</v>
+        <v>956568.5248718999</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>5284422194.661292</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>3458774168.469512</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>7054531909.203349</v>
       </c>
       <c r="L18">
-        <v>47426890698.96482</v>
+        <v>81601274365.53777</v>
       </c>
       <c r="M18">
-        <v>38266053863.0147</v>
+        <v>41108052022.76908</v>
       </c>
       <c r="N18">
-        <v>55834907023.53188</v>
+        <v>127223613807.9627</v>
       </c>
       <c r="O18">
-        <v>47782.13973022057</v>
+        <v>802272.9373560263</v>
       </c>
       <c r="P18">
-        <v>41037.36682772607</v>
+        <v>513927.6107471767</v>
       </c>
       <c r="Q18">
-        <v>54080.52586579061</v>
+        <v>1050675.046540066</v>
       </c>
       <c r="R18">
-        <v>561419.5865093252</v>
+        <v>1253133.438424966</v>
       </c>
       <c r="S18">
-        <v>484747.8274755173</v>
+        <v>635183.0583431993</v>
       </c>
       <c r="T18">
-        <v>633176.436107637</v>
+        <v>1894205.34855547</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>11879255383.43076</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>7609726132.333516</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>15557345414.11877</v>
       </c>
       <c r="X18">
-        <v>74668805005.74025</v>
+        <v>166666747310.5204</v>
       </c>
       <c r="Y18">
-        <v>64471461054.2438</v>
+        <v>84479346759.64551</v>
       </c>
       <c r="Z18">
-        <v>84212466002.31572</v>
+        <v>251929311357.8776</v>
       </c>
       <c r="AA18">
-        <v>0.3648366182461494</v>
+        <v>0.5103925907097434</v>
       </c>
       <c r="AB18">
-        <v>0.4064652291528011</v>
+        <v>0.5133952427481865</v>
       </c>
       <c r="AC18">
-        <v>0.3369757510485859</v>
+        <v>0.4950027326227415</v>
       </c>
     </row>
     <row r="19">
@@ -2094,91 +2094,91 @@
         </is>
       </c>
       <c r="C19">
-        <v>13960.41305161223</v>
+        <v>92665.13976438958</v>
       </c>
       <c r="D19">
-        <v>8480.378690850332</v>
+        <v>64534.29602865379</v>
       </c>
       <c r="E19">
-        <v>19984.99505630456</v>
+        <v>120322.4693931323</v>
       </c>
       <c r="F19">
-        <v>15754.4253960954</v>
+        <v>102715.2150998541</v>
       </c>
       <c r="G19">
-        <v>7059.545718137066</v>
+        <v>52929.6769003886</v>
       </c>
       <c r="H19">
-        <v>28095.58211216867</v>
+        <v>166992.343900231</v>
       </c>
       <c r="I19">
-        <v>777622927.8009059</v>
+        <v>5161633615.155979</v>
       </c>
       <c r="J19">
-        <v>472374053.8377464</v>
+        <v>3594689357.388062</v>
       </c>
       <c r="K19">
-        <v>1113204194.626277</v>
+        <v>6702202190.136301</v>
       </c>
       <c r="L19">
-        <v>2095338577.680689</v>
+        <v>13661123608.28059</v>
       </c>
       <c r="M19">
-        <v>938919580.5122297</v>
+        <v>7039647027.751684</v>
       </c>
       <c r="N19">
-        <v>3736712420.918433</v>
+        <v>22209981738.73072</v>
       </c>
       <c r="O19">
-        <v>38574.49935164709</v>
+        <v>249500.4992293646</v>
       </c>
       <c r="P19">
-        <v>26586.4373874868</v>
+        <v>159859.5691935084</v>
       </c>
       <c r="Q19">
-        <v>49448.46981781944</v>
+        <v>327021.0509900748</v>
       </c>
       <c r="R19">
-        <v>36652.39340397252</v>
+        <v>237849.1381871999</v>
       </c>
       <c r="S19">
-        <v>20047.59142403122</v>
+        <v>119498.1930921545</v>
       </c>
       <c r="T19">
-        <v>56849.12169021871</v>
+        <v>379693.0374372147</v>
       </c>
       <c r="U19">
-        <v>2148676762.885436</v>
+        <v>13897676808.07413</v>
       </c>
       <c r="V19">
-        <v>1480917735.357788</v>
+        <v>8904497723.216824</v>
       </c>
       <c r="W19">
-        <v>2754378665.792172</v>
+        <v>18215726582.24927</v>
       </c>
       <c r="X19">
-        <v>4874768322.728345</v>
+        <v>31633935378.89759</v>
       </c>
       <c r="Y19">
-        <v>2666329659.396152</v>
+        <v>15893259681.25654</v>
       </c>
       <c r="Z19">
-        <v>7560933184.799088</v>
+        <v>50499173979.14955</v>
       </c>
       <c r="AA19">
-        <v>0.5701665312151789</v>
+        <v>0.5681497276689238</v>
       </c>
       <c r="AB19">
-        <v>0.6478606547380685</v>
+        <v>0.557067136073176</v>
       </c>
       <c r="AC19">
-        <v>0.5057868745049985</v>
+        <v>0.5601911875251477</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cancer</t>
+          <t>mort</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2187,91 +2187,91 @@
         </is>
       </c>
       <c r="C20">
-        <v>11169.95247344146</v>
+        <v>60632.75215350388</v>
       </c>
       <c r="D20">
-        <v>2188.889113007589</v>
+        <v>43210.87296639804</v>
       </c>
       <c r="E20">
-        <v>22605.94089883021</v>
+        <v>77837.05823172575</v>
       </c>
       <c r="F20">
-        <v>19678.61126012159</v>
+        <v>907792.5650244171</v>
       </c>
       <c r="G20">
-        <v>2905.515884647718</v>
+        <v>592759.7576164699</v>
       </c>
       <c r="H20">
-        <v>46052.9494353992</v>
+        <v>1213381.78354892</v>
       </c>
       <c r="I20">
-        <v>165393486.2742481</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>32410881.09630337</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>334726166.8889789</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>2617255297.596172</v>
+        <v>120736411148.2475</v>
       </c>
       <c r="M20">
-        <v>386433612.6581466</v>
+        <v>78837047762.99049</v>
       </c>
       <c r="N20">
-        <v>6125042274.908093</v>
+        <v>161379777212.0064</v>
       </c>
       <c r="O20">
-        <v>42258.68551835822</v>
+        <v>171479.5287448698</v>
       </c>
       <c r="P20">
-        <v>-1833.904308357241</v>
+        <v>109965.9427141158</v>
       </c>
       <c r="Q20">
-        <v>85089.41198710834</v>
+        <v>224820.3746579708</v>
       </c>
       <c r="R20">
-        <v>66415.44239852291</v>
+        <v>2069445.607881794</v>
       </c>
       <c r="S20">
-        <v>-2385.865331223808</v>
+        <v>1324810.078433071</v>
       </c>
       <c r="T20">
-        <v>154411.6513993545</v>
+        <v>2709543.880419902</v>
       </c>
       <c r="U20">
-        <v>625724356.4703307</v>
+        <v>0</v>
       </c>
       <c r="V20">
-        <v>-27154621.09384565</v>
+        <v>0</v>
       </c>
       <c r="W20">
-        <v>1259918923.293112</v>
+        <v>0</v>
       </c>
       <c r="X20">
-        <v>8833253839.003548</v>
+        <v>275236265848.2786</v>
       </c>
       <c r="Y20">
-        <v>-317320089.0527664</v>
+        <v>176199740431.5984</v>
       </c>
       <c r="Z20">
-        <v>20536749636.11415</v>
+        <v>360369336095.847</v>
       </c>
       <c r="AA20">
-        <v>0.7037042809706671</v>
+        <v>0.5613353829803724</v>
       </c>
       <c r="AB20">
-        <v>2.217803807542381</v>
+        <v>0.5525700119087552</v>
       </c>
       <c r="AC20">
-        <v>0.7017521086132771</v>
+        <v>0.5521822723310608</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dem</t>
+          <t>diab2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2280,91 +2280,91 @@
         </is>
       </c>
       <c r="C21">
-        <v>3648.474769842909</v>
+        <v>38800.83638920029</v>
       </c>
       <c r="D21">
-        <v>2845.192125985731</v>
+        <v>24963.76886312597</v>
       </c>
       <c r="E21">
-        <v>4409.690087088088</v>
+        <v>52184.27735069978</v>
       </c>
       <c r="F21">
-        <v>7246.102201780566</v>
+        <v>82544.69636917207</v>
       </c>
       <c r="G21">
-        <v>4229.47764730785</v>
+        <v>39037.47692295467</v>
       </c>
       <c r="H21">
-        <v>10358.15891274606</v>
+        <v>141627.6724947709</v>
       </c>
       <c r="I21">
-        <v>61436666.64938486</v>
+        <v>2917861697.304237</v>
       </c>
       <c r="J21">
-        <v>47910190.20947383</v>
+        <v>1877300382.275927</v>
       </c>
       <c r="K21">
-        <v>74254771.37647636</v>
+        <v>3924309841.049982</v>
       </c>
       <c r="L21">
-        <v>963731592.8368154</v>
+        <v>10978444617.09989</v>
       </c>
       <c r="M21">
-        <v>562520527.0919441</v>
+        <v>5191984430.752972</v>
       </c>
       <c r="N21">
-        <v>1377635135.395226</v>
+        <v>18836480441.80453</v>
       </c>
       <c r="O21">
-        <v>11503.68703349809</v>
+        <v>84623.33546324586</v>
       </c>
       <c r="P21">
-        <v>8342.797891455983</v>
+        <v>54157.31808100463</v>
       </c>
       <c r="Q21">
-        <v>14259.34811659477</v>
+        <v>110784.0094240234</v>
       </c>
       <c r="R21">
-        <v>18364.80374344331</v>
+        <v>171444.5677254441</v>
       </c>
       <c r="S21">
-        <v>10699.91313891912</v>
+        <v>81664.2078112544</v>
       </c>
       <c r="T21">
-        <v>25879.40465696505</v>
+        <v>284913.8805347253</v>
       </c>
       <c r="U21">
-        <v>193710585.9570748</v>
+        <v>6363759450.17153</v>
       </c>
       <c r="V21">
-        <v>140484373.6942273</v>
+        <v>4072684477.009662</v>
       </c>
       <c r="W21">
-        <v>240113162.9353394</v>
+        <v>8331068292.695953</v>
       </c>
       <c r="X21">
-        <v>2442518897.877961</v>
+        <v>22802127507.48407</v>
       </c>
       <c r="Y21">
-        <v>1423088447.476243</v>
+        <v>10861339638.89684</v>
       </c>
       <c r="Z21">
-        <v>3441960819.376352</v>
+        <v>37893546111.11846</v>
       </c>
       <c r="AA21">
-        <v>0.6054353586888941</v>
+        <v>0.5185341975876346</v>
       </c>
       <c r="AB21">
-        <v>0.604718506365828</v>
+        <v>0.5219756859311039</v>
       </c>
       <c r="AC21">
-        <v>0.5997528130942411</v>
+        <v>0.5029105909864249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>diab2</t>
+          <t>dem</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2373,85 +2373,85 @@
         </is>
       </c>
       <c r="C22">
-        <v>2711.792120236709</v>
+        <v>16313.52152677028</v>
       </c>
       <c r="D22">
-        <v>-200.8998360724534</v>
+        <v>12202.21959089758</v>
       </c>
       <c r="E22">
-        <v>5420.497659062895</v>
+        <v>20431.31024465632</v>
       </c>
       <c r="F22">
-        <v>5854.117316589164</v>
+        <v>31466.66098866356</v>
       </c>
       <c r="G22">
-        <v>-314.9795863069659</v>
+        <v>17453.23494520813</v>
       </c>
       <c r="H22">
-        <v>14814.53357193394</v>
+        <v>46692.18583311304</v>
       </c>
       <c r="I22">
-        <v>203929479.2339212</v>
+        <v>274703388.9892849</v>
       </c>
       <c r="J22">
-        <v>-15107868.57248455</v>
+        <v>205473175.6911253</v>
       </c>
       <c r="K22">
-        <v>407626844.4591895</v>
+        <v>344042833.2097635</v>
       </c>
       <c r="L22">
-        <v>778597603.1063589</v>
+        <v>4185065911.492253</v>
       </c>
       <c r="M22">
-        <v>-41892284.97882646</v>
+        <v>2321280247.712681</v>
       </c>
       <c r="N22">
-        <v>1970332965.067214</v>
+        <v>6210060715.804034</v>
       </c>
       <c r="O22">
-        <v>10168.87727611247</v>
+        <v>50991.04366433024</v>
       </c>
       <c r="P22">
-        <v>87.55817049086444</v>
+        <v>32730.12392153444</v>
       </c>
       <c r="Q22">
-        <v>17975.13331873855</v>
+        <v>66901.10201511951</v>
       </c>
       <c r="R22">
-        <v>20643.40380571091</v>
+        <v>82182.57239572945</v>
       </c>
       <c r="S22">
-        <v>135.7767855582018</v>
+        <v>42232.23829081892</v>
       </c>
       <c r="T22">
-        <v>46308.36267309635</v>
+        <v>122683.4296259731</v>
       </c>
       <c r="U22">
-        <v>764709740.0409356</v>
+        <v>858638184.2636615</v>
       </c>
       <c r="V22">
-        <v>6584461.979083515</v>
+        <v>551142556.7147171</v>
       </c>
       <c r="W22">
-        <v>1351748000.702454</v>
+        <v>1126547656.832593</v>
       </c>
       <c r="X22">
-        <v>2745572706.159552</v>
+        <v>10930282128.63202</v>
       </c>
       <c r="Y22">
-        <v>18058312.47924083</v>
+        <v>5616887692.678916</v>
       </c>
       <c r="Z22">
-        <v>6159012235.521814</v>
+        <v>16316896140.25442</v>
       </c>
       <c r="AA22">
-        <v>0.7164170515828574</v>
+        <v>0.6171127275361522</v>
       </c>
       <c r="AB22">
-        <v>3.319833873014673</v>
+        <v>0.5867319457467076</v>
       </c>
       <c r="AC22">
-        <v>0.6800894543278529</v>
+        <v>0.6194091901778077</v>
       </c>
     </row>
   </sheetData>
